--- a/resources/templates/import/template-nasabah-prioritas-bod-boc.xlsx
+++ b/resources/templates/import/template-nasabah-prioritas-bod-boc.xlsx
@@ -1,21 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29127"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Danang\Downloads\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2795EB4C-6FF9-4859-8618-EB31B939384F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView activeTab="0" autoFilterDateGrouping="true" firstSheet="0" minimized="false" showHorizontalScroll="true" showSheetTabs="true" showVerticalScroll="true" tabRatio="600" visibility="visible"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Nasabah Prioritas" sheetId="1" r:id="rId4"/>
+    <sheet name="Nasabah Prioritas" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="999999" calcMode="auto" calcCompleted="1" fullCalcOnLoad="0" forceFullCalc="0"/>
+  <calcPr calcId="191029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
   <si>
     <t>nama_nasabah</t>
   </si>
@@ -23,47 +28,39 @@
     <t>cif</t>
   </si>
   <si>
-    <t>bod_boc</t>
-  </si>
-  <si>
-    <t>jabatan</t>
-  </si>
-  <si>
     <t>unit_kerja</t>
   </si>
   <si>
-    <t>status_nasabah</t>
-  </si>
-  <si>
-    <t>produk_1</t>
-  </si>
-  <si>
-    <t>produk_2</t>
-  </si>
-  <si>
-    <t>keterangan</t>
+    <t>instansi</t>
+  </si>
+  <si>
+    <t>bod/boc</t>
+  </si>
+  <si>
+    <t>ket_nasabah</t>
+  </si>
+  <si>
+    <t>fasilitas_1</t>
+  </si>
+  <si>
+    <t>fasilitas_2</t>
+  </si>
+  <si>
+    <t>fasilitas_3</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
-      <b val="0"/>
-      <i val="0"/>
-      <strike val="0"/>
-      <u val="none"/>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
     </font>
     <font>
-      <b val="1"/>
-      <i val="0"/>
-      <strike val="0"/>
-      <u val="none"/>
+      <b/>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
@@ -90,14 +87,22 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
-    <xf xfId="0" fontId="1" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotTableStyle1"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -387,42 +392,38 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:I1"/>
-  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="15.282" bestFit="true" customWidth="true" style="0"/>
-    <col min="2" max="2" width="4.57" bestFit="true" customWidth="true" style="0"/>
-    <col min="3" max="3" width="9.283" bestFit="true" customWidth="true" style="0"/>
-    <col min="4" max="4" width="9.283" bestFit="true" customWidth="true" style="0"/>
-    <col min="5" max="5" width="12.854" bestFit="true" customWidth="true" style="0"/>
-    <col min="6" max="6" width="17.567" bestFit="true" customWidth="true" style="0"/>
-    <col min="7" max="7" width="10.569" bestFit="true" customWidth="true" style="0"/>
-    <col min="8" max="8" width="10.569" bestFit="true" customWidth="true" style="0"/>
-    <col min="9" max="9" width="12.854" bestFit="true" customWidth="true" style="0"/>
+    <col min="1" max="1" width="15.26953125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.08984375" customWidth="1"/>
+    <col min="3" max="3" width="18.7265625" customWidth="1"/>
+    <col min="4" max="4" width="17.1796875" customWidth="1"/>
+    <col min="5" max="5" width="12.81640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.54296875" customWidth="1"/>
+    <col min="7" max="8" width="10.54296875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="D1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>6</v>
@@ -435,8 +436,14 @@
       </c>
     </row>
   </sheetData>
-  <printOptions gridLines="false" gridLinesSet="true"/>
+  <dataValidations count="2">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2:B1048576" xr:uid="{D0C1DD70-EC2C-4138-86A9-56960BE0840C}">
+      <formula1>"BOD,BOC"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D1048576" xr:uid="{48E23B9B-F9BB-4320-ADAC-03B8B78FD3FF}">
+      <formula1>"Sudah Nasabah,Belum Nasabah"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>
 </worksheet>
 </file>
--- a/resources/templates/import/template-nasabah-prioritas-bod-boc.xlsx
+++ b/resources/templates/import/template-nasabah-prioritas-bod-boc.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Danang\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\project-ABAH\resources\templates\import\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2795EB4C-6FF9-4859-8618-EB31B939384F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19B491B1-C8F4-46CD-912F-28797D035D26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,15 +20,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
   <si>
     <t>nama_nasabah</t>
   </si>
   <si>
     <t>cif</t>
-  </si>
-  <si>
-    <t>unit_kerja</t>
   </si>
   <si>
     <t>instansi</t>
@@ -66,15 +63,21 @@
       <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -82,13 +85,31 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -393,50 +414,146 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I1"/>
+  <dimension ref="A1:H11"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="15.26953125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="13.08984375" customWidth="1"/>
     <col min="3" max="3" width="18.7265625" customWidth="1"/>
     <col min="4" max="4" width="17.1796875" customWidth="1"/>
-    <col min="5" max="5" width="12.81640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.54296875" customWidth="1"/>
-    <col min="7" max="8" width="10.54296875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="12.81640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.54296875" customWidth="1"/>
+    <col min="6" max="7" width="10.54296875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
-        <v>8</v>
-      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A3" s="1"/>
+      <c r="B3" s="1"/>
+      <c r="C3" s="1"/>
+      <c r="D3" s="1"/>
+      <c r="E3" s="1"/>
+      <c r="F3" s="1"/>
+      <c r="G3" s="1"/>
+      <c r="H3" s="1"/>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A4" s="1"/>
+      <c r="B4" s="1"/>
+      <c r="C4" s="1"/>
+      <c r="D4" s="1"/>
+      <c r="E4" s="1"/>
+      <c r="F4" s="1"/>
+      <c r="G4" s="1"/>
+      <c r="H4" s="1"/>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A5" s="1"/>
+      <c r="B5" s="1"/>
+      <c r="C5" s="1"/>
+      <c r="D5" s="1"/>
+      <c r="E5" s="1"/>
+      <c r="F5" s="1"/>
+      <c r="G5" s="1"/>
+      <c r="H5" s="1"/>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A6" s="1"/>
+      <c r="B6" s="1"/>
+      <c r="C6" s="1"/>
+      <c r="D6" s="1"/>
+      <c r="E6" s="1"/>
+      <c r="F6" s="1"/>
+      <c r="G6" s="1"/>
+      <c r="H6" s="1"/>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A7" s="1"/>
+      <c r="B7" s="1"/>
+      <c r="C7" s="1"/>
+      <c r="D7" s="1"/>
+      <c r="E7" s="1"/>
+      <c r="F7" s="1"/>
+      <c r="G7" s="1"/>
+      <c r="H7" s="1"/>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A8" s="1"/>
+      <c r="B8" s="1"/>
+      <c r="C8" s="1"/>
+      <c r="D8" s="1"/>
+      <c r="E8" s="1"/>
+      <c r="F8" s="1"/>
+      <c r="G8" s="1"/>
+      <c r="H8" s="1"/>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A9" s="1"/>
+      <c r="B9" s="1"/>
+      <c r="C9" s="1"/>
+      <c r="D9" s="1"/>
+      <c r="E9" s="1"/>
+      <c r="F9" s="1"/>
+      <c r="G9" s="1"/>
+      <c r="H9" s="1"/>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A10" s="1"/>
+      <c r="B10" s="1"/>
+      <c r="C10" s="1"/>
+      <c r="D10" s="1"/>
+      <c r="E10" s="1"/>
+      <c r="F10" s="1"/>
+      <c r="G10" s="1"/>
+      <c r="H10" s="1"/>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A11" s="1"/>
+      <c r="B11" s="1"/>
+      <c r="C11" s="1"/>
+      <c r="D11" s="1"/>
+      <c r="E11" s="1"/>
+      <c r="F11" s="1"/>
+      <c r="G11" s="1"/>
+      <c r="H11" s="1"/>
     </row>
   </sheetData>
-  <dataValidations count="2">
+  <dataValidations disablePrompts="1" count="2">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2:B1048576" xr:uid="{D0C1DD70-EC2C-4138-86A9-56960BE0840C}">
       <formula1>"BOD,BOC"</formula1>
     </dataValidation>

--- a/resources/templates/import/template-nasabah-prioritas-bod-boc.xlsx
+++ b/resources/templates/import/template-nasabah-prioritas-bod-boc.xlsx
@@ -1,40 +1,37 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29127"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr codeName="ThisWorkbook"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\project-ABAH\resources\templates\import\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19B491B1-C8F4-46CD-912F-28797D035D26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView activeTab="0" autoFilterDateGrouping="true" firstSheet="0" minimized="false" showHorizontalScroll="true" showSheetTabs="true" showVerticalScroll="true" tabRatio="600" visibility="visible"/>
   </bookViews>
   <sheets>
-    <sheet name="Nasabah Prioritas" sheetId="1" r:id="rId1"/>
+    <sheet name="Nasabah Prioritas" sheetId="1" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Nasabah Prioritas'!$A$1:$H$1</definedName>
+  </definedNames>
+  <calcPr calcId="999999" calcMode="auto" calcCompleted="1" fullCalcOnLoad="0" forceFullCalc="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="8">
+  <si>
+    <t>instansi</t>
+  </si>
+  <si>
+    <t>bod/boc</t>
+  </si>
   <si>
     <t>nama_nasabah</t>
   </si>
   <si>
+    <t>ket_nasabah</t>
+  </si>
+  <si>
     <t>cif</t>
-  </si>
-  <si>
-    <t>instansi</t>
-  </si>
-  <si>
-    <t>bod/boc</t>
-  </si>
-  <si>
-    <t>ket_nasabah</t>
   </si>
   <si>
     <t>fasilitas_1</t>
@@ -49,17 +46,25 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="2">
     <font>
+      <b val="0"/>
+      <i val="0"/>
+      <strike val="0"/>
+      <u val="none"/>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
     </font>
     <font>
-      <b/>
+      <b val="1"/>
+      <i val="0"/>
+      <strike val="0"/>
+      <u val="none"/>
       <sz val="11"/>
-      <color rgb="FF000000"/>
+      <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
     </font>
   </fonts>
@@ -72,12 +77,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="3" tint="0.59999389629810485"/>
-        <bgColor indexed="64"/>
+        <fgColor rgb="FF355FB3"/>
+        <bgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -87,16 +92,31 @@
     </border>
     <border>
       <left style="thin">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </left>
       <right style="thin">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </right>
       <top style="thin">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </top>
       <bottom style="thin">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF27498A"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF27498A"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF27498A"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF27498A"/>
       </bottom>
       <diagonal/>
     </border>
@@ -105,25 +125,17 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="3">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="1" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="0"/>
+    <xf xfId="0" fontId="1" numFmtId="0" fillId="2" borderId="2" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <tableStyles defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotTableStyle1"/>
 </styleSheet>
 </file>
 
@@ -413,34 +425,38 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr filterMode="1">
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+  </sheetPr>
   <dimension ref="A1:H11"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="15.26953125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.08984375" customWidth="1"/>
-    <col min="3" max="3" width="18.7265625" customWidth="1"/>
-    <col min="4" max="4" width="17.1796875" customWidth="1"/>
-    <col min="5" max="5" width="12.54296875" customWidth="1"/>
-    <col min="6" max="7" width="10.54296875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.81640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.282" bestFit="true" customWidth="true" style="0"/>
+    <col min="2" max="2" width="13.997" bestFit="true" customWidth="true" style="0"/>
+    <col min="3" max="3" width="19.995" bestFit="true" customWidth="true" style="0"/>
+    <col min="4" max="4" width="18.71" bestFit="true" customWidth="true" style="0"/>
+    <col min="5" max="5" width="9.283" bestFit="true" customWidth="true" style="0"/>
+    <col min="6" max="6" width="18.71" bestFit="true" customWidth="true" style="0"/>
+    <col min="7" max="7" width="18.71" bestFit="true" customWidth="true" style="0"/>
+    <col min="8" max="8" width="18.71" bestFit="true" customWidth="true" style="0"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:8" customHeight="1" ht="24">
       <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="D1" s="2" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>1</v>
       </c>
       <c r="F1" s="2" t="s">
         <v>5</v>
@@ -452,7 +468,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:8">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -462,7 +478,7 @@
       <c r="G2" s="1"/>
       <c r="H2" s="1"/>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:8">
       <c r="A3" s="1"/>
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
@@ -472,7 +488,7 @@
       <c r="G3" s="1"/>
       <c r="H3" s="1"/>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:8">
       <c r="A4" s="1"/>
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
@@ -482,7 +498,7 @@
       <c r="G4" s="1"/>
       <c r="H4" s="1"/>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:8">
       <c r="A5" s="1"/>
       <c r="B5" s="1"/>
       <c r="C5" s="1"/>
@@ -492,7 +508,7 @@
       <c r="G5" s="1"/>
       <c r="H5" s="1"/>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:8">
       <c r="A6" s="1"/>
       <c r="B6" s="1"/>
       <c r="C6" s="1"/>
@@ -502,7 +518,7 @@
       <c r="G6" s="1"/>
       <c r="H6" s="1"/>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:8">
       <c r="A7" s="1"/>
       <c r="B7" s="1"/>
       <c r="C7" s="1"/>
@@ -512,7 +528,7 @@
       <c r="G7" s="1"/>
       <c r="H7" s="1"/>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:8">
       <c r="A8" s="1"/>
       <c r="B8" s="1"/>
       <c r="C8" s="1"/>
@@ -522,7 +538,7 @@
       <c r="G8" s="1"/>
       <c r="H8" s="1"/>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:8">
       <c r="A9" s="1"/>
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
@@ -532,7 +548,7 @@
       <c r="G9" s="1"/>
       <c r="H9" s="1"/>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:8">
       <c r="A10" s="1"/>
       <c r="B10" s="1"/>
       <c r="C10" s="1"/>
@@ -542,7 +558,7 @@
       <c r="G10" s="1"/>
       <c r="H10" s="1"/>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:8">
       <c r="A11" s="1"/>
       <c r="B11" s="1"/>
       <c r="C11" s="1"/>
@@ -553,14 +569,17 @@
       <c r="H11" s="1"/>
     </row>
   </sheetData>
-  <dataValidations disablePrompts="1" count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2:B1048576" xr:uid="{D0C1DD70-EC2C-4138-86A9-56960BE0840C}">
+  <autoFilter ref="A1:H1"/>
+  <dataValidations count="2">
+    <dataValidation type="list" operator="between" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="B2:B1048576">
       <formula1>"BOD,BOC"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D1048576" xr:uid="{48E23B9B-F9BB-4320-ADAC-03B8B78FD3FF}">
+    <dataValidation type="list" operator="between" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="D2:D1048576">
       <formula1>"Sudah Nasabah,Belum Nasabah"</formula1>
     </dataValidation>
   </dataValidations>
+  <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>
 </worksheet>
 </file>